--- a/株式会社鶴岡中央青果/案件マスター_鶴岡中央青果_261019.xlsx
+++ b/株式会社鶴岡中央青果/案件マスター_鶴岡中央青果_261019.xlsx
@@ -2235,7 +2235,7 @@
       </c>
       <c r="C24" s="31" t="inlineStr">
         <is>
-          <t>6時〜（終業時刻は要確認）／水・日・祝日</t>
+          <t>5時〜（終業時刻は要確認）／水・日・祝日</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
     <row r="11">
       <c r="B11" s="47" t="inlineStr">
         <is>
-          <t>※営業時間は早朝6時から（終業時刻は要確認）、定休日は水・日・祝日（法人事業概況説明書）。車両等はリースを利用（リース料年6,227千円、対象資産は要確認）。</t>
+          <t>※営業時間は早朝5時から（終業時刻は要確認）、定休日は水・日・祝日。リース料年6,227千円を計上（対象資産・車両の保有形態は要確認）。</t>
         </is>
       </c>
     </row>
@@ -13764,7 +13764,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="24" customHeight="1">
       <c r="B13" s="27" t="inlineStr">
         <is>
           <t>営業時間・定休日</t>
@@ -13772,8 +13772,7 @@
       </c>
       <c r="C13" s="28" t="inlineStr">
         <is>
-          <t>・早朝（5〜6時）から営業。終業時刻は要確認
-・定休日は水曜・祝日等（法人事業概況説明書では水・日・祝。日曜の扱いは要確認）</t>
+          <t>・早朝5時から営業（終業時刻は要確認）／定休日は水・日・祝日</t>
         </is>
       </c>
     </row>
@@ -14727,7 +14726,7 @@
       </c>
       <c r="D38" s="74" t="inlineStr">
         <is>
-          <t>営業時間（5時からとの発言）・定休日（水曜・祝日との発言、概況説明書は水・日・祝）</t>
+          <t>営業時間（5時からとの発言、概況説明書は6時）・定休日（水曜・祝日との発言、概況説明書は水・日・祝）</t>
         </is>
       </c>
       <c r="E38" s="74" t="inlineStr">
@@ -14737,7 +14736,7 @@
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>要確認</t>
+          <t>確定（10/19 田垣内）：営業時間は5時から、定休日は水・日・祝日で記載</t>
         </is>
       </c>
     </row>

--- a/株式会社鶴岡中央青果/案件マスター_鶴岡中央青果_261019.xlsx
+++ b/株式会社鶴岡中央青果/案件マスター_鶴岡中央青果_261019.xlsx
@@ -1510,7 +1510,7 @@
       </c>
       <c r="C5" s="19">
         <f>修正PL!E21</f>
-        <v>696266.620500001</v>
+        <v>10443146.6205</v>
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
@@ -1580,15 +1580,15 @@
       </c>
       <c r="C10" s="9">
         <f>MAX($C$5,0)*C8</f>
-        <v>696266.620500001</v>
+        <v>10443146.6205</v>
       </c>
       <c r="D10" s="9">
         <f>MAX($C$5,0)*D8</f>
-        <v>1392533.241</v>
+        <v>20886293.241</v>
       </c>
       <c r="E10" s="9">
         <f>MAX($C$5,0)*E8</f>
-        <v>2088799.8615</v>
+        <v>31329439.8615</v>
       </c>
     </row>
     <row r="11">
@@ -1599,15 +1599,15 @@
       </c>
       <c r="C11" s="13">
         <f>C9+C10</f>
-        <v>56014724.0490715</v>
+        <v>65761604.0490715</v>
       </c>
       <c r="D11" s="13">
         <f>D9+D10</f>
-        <v>56710990.6695715</v>
+        <v>76204750.6695715</v>
       </c>
       <c r="E11" s="13">
         <f>E9+E10</f>
-        <v>57407257.2900715</v>
+        <v>86647897.2900715</v>
       </c>
     </row>
     <row r="13">
@@ -1625,7 +1625,7 @@
       </c>
       <c r="C15" s="19">
         <f>C5-修正PL!E10*(1-0.34)*0.5</f>
-        <v>2915326.458</v>
+        <v>12662206.458</v>
       </c>
     </row>
     <row r="16">
@@ -1636,15 +1636,15 @@
       </c>
       <c r="C16" s="9">
         <f>$C$4+MAX($C$15,0)*C8</f>
-        <v>58233783.8865715</v>
+        <v>67980663.8865715</v>
       </c>
       <c r="D16" s="9">
         <f>$C$4+MAX($C$15,0)*D8</f>
-        <v>61149110.3445715</v>
+        <v>80642870.3445715</v>
       </c>
       <c r="E16" s="9">
         <f>$C$4+MAX($C$15,0)*E8</f>
-        <v>64064436.8025715</v>
+        <v>93305076.8025715</v>
       </c>
     </row>
   </sheetData>
@@ -1691,7 +1691,7 @@
       </c>
       <c r="C4" s="19">
         <f>修正PL!E22</f>
-        <v>11994440.425</v>
+        <v>26762440.425</v>
       </c>
     </row>
     <row r="5">
@@ -1763,15 +1763,15 @@
       </c>
       <c r="C10" s="9">
         <f>$C$4*C9</f>
-        <v>35983321.275</v>
+        <v>80287321.275</v>
       </c>
       <c r="D10" s="9">
         <f>$C$4*D9</f>
-        <v>47977761.7</v>
+        <v>107049761.7</v>
       </c>
       <c r="E10" s="9">
         <f>$C$4*E9</f>
-        <v>59972202.125</v>
+        <v>133812202.125</v>
       </c>
     </row>
     <row r="11">
@@ -1782,15 +1782,15 @@
       </c>
       <c r="C11" s="9">
         <f>-C10*$C$6</f>
-        <v>-10794996.3825</v>
+        <v>-24086196.3825</v>
       </c>
       <c r="D11" s="9">
         <f>-D10*$C$6</f>
-        <v>-14393328.51</v>
+        <v>-32114928.51</v>
       </c>
       <c r="E11" s="9">
         <f>-E10*$C$6</f>
-        <v>-17991660.6375</v>
+        <v>-40143660.6375</v>
       </c>
     </row>
     <row r="12">
@@ -1820,15 +1820,15 @@
       </c>
       <c r="C13" s="13">
         <f>SUM(C10:C12)</f>
-        <v>-118391898.1075</v>
+        <v>-87379098.1075</v>
       </c>
       <c r="D13" s="13">
         <f>SUM(D10:D12)</f>
-        <v>-109995789.81</v>
+        <v>-68645389.81</v>
       </c>
       <c r="E13" s="13">
         <f>SUM(E10:E12)</f>
-        <v>-101599681.5125</v>
+        <v>-49911681.5125</v>
       </c>
     </row>
     <row r="15">
@@ -1911,11 +1911,11 @@
       </c>
       <c r="C5" s="9">
         <f>年買法!C11</f>
-        <v>56014724.0490715</v>
+        <v>65761604.0490715</v>
       </c>
       <c r="D5" s="9">
         <f>年買法!E11</f>
-        <v>57407257.2900715</v>
+        <v>86647897.2900715</v>
       </c>
       <c r="E5" s="20" t="inlineStr">
         <is>
@@ -1931,11 +1931,11 @@
       </c>
       <c r="C6" s="9">
         <f>'EV EBITDAマルチプル'!C13</f>
-        <v>-118391898.1075</v>
+        <v>-87379098.1075</v>
       </c>
       <c r="D6" s="9">
         <f>'EV EBITDAマルチプル'!E13</f>
-        <v>-101599681.5125</v>
+        <v>-49911681.5125</v>
       </c>
       <c r="E6" s="20" t="inlineStr">
         <is>
@@ -2156,7 +2156,7 @@
       </c>
       <c r="C16" s="28" t="str">
         <f>TEXT(PLハイライト!C43/1000,"#,##0")&amp;"千円（過去3期平均）"</f>
-        <v>14,549千円（過去3期平均）</v>
+        <v>29,317千円（過去3期平均）</v>
       </c>
     </row>
     <row r="17" ht="17" customHeight="1">
@@ -2626,15 +2626,15 @@
       </c>
       <c r="C19" s="41">
         <f>SUM(C20:C23)</f>
-        <v>5273508</v>
+        <v>20041508</v>
       </c>
       <c r="D19" s="41">
         <f>SUM(D20:D23)</f>
-        <v>5467707</v>
+        <v>20235707</v>
       </c>
       <c r="E19" s="41">
         <f>SUM(E20:E23)</f>
-        <v>-8388975.75</v>
+        <v>6379024.25</v>
       </c>
       <c r="F19" s="41" t="inlineStr">
         <is>
@@ -2650,15 +2650,15 @@
       </c>
       <c r="C20" s="39">
         <f>修正PL!C9</f>
-        <v>3082000</v>
+        <v>17850000</v>
       </c>
       <c r="D20" s="39">
         <f>修正PL!D9</f>
-        <v>3082000</v>
+        <v>17850000</v>
       </c>
       <c r="E20" s="39">
         <f>修正PL!E9</f>
-        <v>-4094000</v>
+        <v>10674000</v>
       </c>
       <c r="F20" s="39" t="inlineStr">
         <is>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="G20" s="31" t="inlineStr">
         <is>
-          <t>代表者・配偶者の報酬を新体制の役員報酬（仮定8,000千円）に置換。社会保険料15%を連動</t>
+          <t>譲渡時に退任する役員（代表者・配偶者・監査役）と退任済みの常務取締役の報酬を全額控除（社保15%連動）し、代表者の顧問料（月18万円）を計上</t>
         </is>
       </c>
     </row>
@@ -2725,7 +2725,7 @@
       </c>
       <c r="G22" s="31" t="inlineStr">
         <is>
-          <t>仕入先市場から受け取る完納奨励金（期限内の代金支払に対する奨励金。保証金として積立：代表者談）。毎期経常的に発生するため加算</t>
+          <t>毎期経常的に発生する事業関連収益として加算（受取奨励金の内容は要確認）</t>
         </is>
       </c>
     </row>
@@ -2773,15 +2773,15 @@
       </c>
       <c r="C25" s="44">
         <f>C10+C17+C19</f>
-        <v>23693940</v>
+        <v>38461940</v>
       </c>
       <c r="D25" s="44">
         <f>D10+D17+D19</f>
-        <v>13602331</v>
+        <v>28370331</v>
       </c>
       <c r="E25" s="44">
         <f>E10+E17+E19</f>
-        <v>6349906.25</v>
+        <v>21117906.25</v>
       </c>
       <c r="F25" s="44" t="inlineStr">
         <is>
@@ -3002,7 +3002,7 @@
       </c>
       <c r="C43" s="39">
         <f>AVERAGE(C25:E25)</f>
-        <v>14548725.75</v>
+        <v>29316725.75</v>
       </c>
     </row>
     <row r="44">
@@ -3013,7 +3013,7 @@
       </c>
       <c r="C44" s="39">
         <f>AVERAGE(D25:E25)</f>
-        <v>9976118.625</v>
+        <v>24744118.625</v>
       </c>
     </row>
     <row r="46">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="E10" s="28" t="inlineStr">
         <is>
-          <t>完納奨励金：期限内に代金を支払った八百屋等へ対象売上の約3%を還元（市場の商慣習）</t>
+          <t>完納奨励金：期限内に代金を支払った八百屋等へ支給（市場の商慣習）</t>
         </is>
       </c>
     </row>
@@ -7243,7 +7243,7 @@
     <row r="11">
       <c r="B11" s="47" t="inlineStr">
         <is>
-          <t>※営業時間は早朝5時から（終業時刻は要確認）、定休日は水・日・祝日。リース料年6,227千円を計上（対象資産・車両の保有形態は要確認）。</t>
+          <t>※営業時間は早朝5時から（終業時刻は要確認）、定休日は水・日・祝日。車両は自己所有とリースを併用（リース料年6,227千円）。</t>
         </is>
       </c>
     </row>
@@ -9152,7 +9152,7 @@
       </c>
       <c r="I42" s="88" t="inlineStr">
         <is>
-          <t>備忘価額のみ。集配車両はリースと推察（要確認）</t>
+          <t>備忘価額のみ（償却済）。車両は自己所有とリースを併用</t>
         </is>
       </c>
     </row>
@@ -13696,7 +13696,7 @@
       </c>
       <c r="C7" s="28" t="inlineStr">
         <is>
-          <t>・保証金33,303千円は仕入先市場への仕入代金のデポジット（約10日分）。受領した完納奨励金の積立により増加。取引終了時に返金される
+          <t>・保証金33,303千円は仕入代金のデポジット（約10日分）。取引終了時に返金される
 ・預り保証金8,980千円は販売先（八百屋等）からの預り（1先あたり5〜30万円程度）</t>
         </is>
       </c>
@@ -13710,7 +13710,7 @@
       <c r="C8" s="28" t="inlineStr">
         <is>
           <t>・受託販売手数料は8.5%（市場で一般的な水準。県への届出等で変更可能だが据置）
-・完納奨励金：期限内に代金を支払った販売先へ対象売上の約3%を還元（売上割戻）。仕入先市場からも同様に受領（受取奨励金）</t>
+・売上割戻は期限内に代金を支払った八百屋等への完納奨励金（市場業界の商慣習）</t>
         </is>
       </c>
     </row>
@@ -13833,7 +13833,7 @@
     <row r="2">
       <c r="A2" s="5" t="inlineStr">
         <is>
-          <t>最終更新：2026年10月19日（第2回面談〔2026/10/16往訪・岡部社長〕のメモ・文字起こしを反映）。★＝面談で特に重要とした論点</t>
+          <t>最終更新：2026年10月19日（第2回面談〔2026/10/16往訪〕のメモ・文字起こし、田垣内確認事項を反映）。★＝面談で特に重要とした論点</t>
         </is>
       </c>
     </row>
@@ -14111,7 +14111,7 @@
       </c>
       <c r="F13" s="20" t="inlineStr">
         <is>
-          <t>回答済：隣の市場（仕入先）への仕入代金のデポジット（約10日分）で取引終了時に返金。受領する完納奨励金を積み立てて増加したとの説明（受取奨励金の会計処理は要確認）。預り保証金は販売先（八百屋等）から1先5〜30万円程度</t>
+          <t>回答済：仕入代金に対するデポジット（約10日分）で取引終了時に返金。預り保証金は販売先（八百屋等）から1先5〜30万円程度</t>
         </is>
       </c>
     </row>
@@ -14586,7 +14586,7 @@
       </c>
       <c r="F32" s="20" t="inlineStr">
         <is>
-          <t>売上割戻は回答済。受取奨励金の内容は要確認</t>
+          <t>売上割戻は回答済。受取奨励金（毎期約2.3〜2.5百万円）の内容は要確認</t>
         </is>
       </c>
     </row>
@@ -14611,7 +14611,7 @@
       </c>
       <c r="F33" s="20" t="inlineStr">
         <is>
-          <t>要検討：現行の修正PLは代表者・配偶者報酬を新体制の役員報酬8,000千円（仮定）に置換。顧問料を加味するかは買手の体制次第（評価書は未変更）</t>
+          <t>決定（10/19 田垣内）：退任役員（代表者・配偶者・監査役・退任済み常務）の報酬は全額控除し、代表者は半額（月18万円）の顧問料を計上。修正PL・評価書・概要書に反映済み</t>
         </is>
       </c>
     </row>
@@ -14626,7 +14626,7 @@
       </c>
       <c r="D34" s="74" t="inlineStr">
         <is>
-          <t>★希望価格（最低1.1億円）と評価書の株式価値（年買法56,015〜57,407千円）の乖離</t>
+          <t>★希望価格（最低1.1億円）と評価書の株式価値（年買法）の乖離</t>
         </is>
       </c>
       <c r="E34" s="74" t="inlineStr">
@@ -14634,10 +14634,9 @@
           <t>高</t>
         </is>
       </c>
-      <c r="F34" s="20" t="inlineStr">
-        <is>
-          <t>要検討：不動産の時価再評価（田垣内）、足元の利益改善（9月試算表）を反映した正常収益力の見直しで、乖離の説明材料を整理する</t>
-        </is>
+      <c r="F34" s="20" t="str">
+        <f>"役員報酬の正常化方針の変更後、年買法は"&amp;TEXT(年買法!C11/1000,"#,##0")&amp;"〜"&amp;TEXT(年買法!E11/1000,"#,##0")&amp;"千円。不動産の時価再評価・9月試算表で引き続き乖離を検証"</f>
+        <v>役員報酬の正常化方針の変更後、年買法は65,762〜86,648千円。不動産の時価再評価・9月試算表で引き続き乖離を検証</v>
       </c>
     </row>
     <row r="35">
@@ -14651,7 +14650,7 @@
       </c>
       <c r="D35" s="74" t="inlineStr">
         <is>
-          <t>完納奨励金の還元率（対象売上の約3%：代表者談）と売上割戻の計上額（2026/3期1,637千円＝売上高の0.14%）の整合</t>
+          <t>完納奨励金の内容（文字起こしでは「売上の約3%を還元」「保証金は完納奨励金の積立」との記載）</t>
         </is>
       </c>
       <c r="E35" s="74" t="inlineStr">
@@ -14661,7 +14660,7 @@
       </c>
       <c r="F35" s="20" t="inlineStr">
         <is>
-          <t>要確認：対象先・対象売上の範囲</t>
+          <t>解決（10/19 田垣内）：ヒアリングメモの内容（期限内に代金を支払った八百屋等へ支給する完納奨励金＝売上割戻）が正。約3%・保証金への積立は採用しない</t>
         </is>
       </c>
     </row>
@@ -14701,7 +14700,7 @@
       </c>
       <c r="D37" s="74" t="inlineStr">
         <is>
-          <t>配送先の店舗数が以前の12店舗から6店舗に減少したとの発言（どの取引先か文字起こしからは不明確）</t>
+          <t>★(株)主婦の店の店舗数が以前の12店舗から6店舗に減少（センター費・売上への影響）</t>
         </is>
       </c>
       <c r="E37" s="74" t="inlineStr">
@@ -14711,7 +14710,7 @@
       </c>
       <c r="F37" s="20" t="inlineStr">
         <is>
-          <t>要確認：取引先と売上への影響</t>
+          <t>回答済（10/19 田垣内）：主婦の店。売上・センター費への影響額は要確認</t>
         </is>
       </c>
     </row>
@@ -14726,7 +14725,7 @@
       </c>
       <c r="D38" s="74" t="inlineStr">
         <is>
-          <t>営業時間（5時からとの発言、概況説明書は6時）・定休日（水曜・祝日との発言、概況説明書は水・日・祝）</t>
+          <t>営業時間（5時からとの発言）・定休日（水曜・祝日との発言、概況説明書は水・日・祝）</t>
         </is>
       </c>
       <c r="E38" s="74" t="inlineStr">
@@ -14736,7 +14735,7 @@
       </c>
       <c r="F38" s="20" t="inlineStr">
         <is>
-          <t>確定（10/19 田垣内）：営業時間は5時から、定休日は水・日・祝日で記載</t>
+          <t>要確認</t>
         </is>
       </c>
     </row>
@@ -14761,7 +14760,7 @@
       </c>
       <c r="F39" s="20" t="inlineStr">
         <is>
-          <t>要確認（文字起こしでは不明瞭）</t>
+          <t>回答済（10/19 田垣内）：自己所有とリースを併用。リース契約一覧は依頼中</t>
         </is>
       </c>
     </row>
@@ -18337,42 +18336,42 @@
     <row r="7">
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>（前提）代表者及びその家族分の役員報酬（実績）</t>
+          <t>（前提）退任役員の役員報酬（実績）</t>
         </is>
       </c>
       <c r="C7" s="9" t="n">
-        <v>10680000</v>
+        <v>17400000</v>
       </c>
       <c r="D7" s="9" t="n">
-        <v>10680000</v>
+        <v>17400000</v>
       </c>
       <c r="E7" s="9" t="n">
-        <v>4440000</v>
+        <v>11160000</v>
       </c>
       <c r="F7" s="20" t="inlineStr">
         <is>
-          <t>勘定科目内訳書「人件費の内訳」（代表取締役・取締役〔配偶者〕）</t>
+          <t>勘定科目内訳書（役員給与等）。代表取締役・取締役〔配偶者〕・監査役・常務取締役〔2026/5退任済〕。取締役〔代表者の弟〕は残留のため対象外</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>（前提）新体制の役員報酬（仮定）</t>
+          <t>（前提）代表者の顧問料（退任後）</t>
         </is>
       </c>
       <c r="C8" s="9" t="n">
-        <v>8000000</v>
+        <v>2160000</v>
       </c>
       <c r="D8" s="9" t="n">
-        <v>8000000</v>
+        <v>2160000</v>
       </c>
       <c r="E8" s="9" t="n">
-        <v>8000000</v>
+        <v>2160000</v>
       </c>
       <c r="F8" s="20" t="inlineStr">
         <is>
-          <t>（仮定）買手からの派遣役員等を年8,000千円と想定</t>
+          <t>代表者の現行報酬（月36万円）の半額＝月18万円（10/16面談で合意）。顧問料のため社会保険料は連動させない</t>
         </is>
       </c>
     </row>
@@ -18383,20 +18382,20 @@
         </is>
       </c>
       <c r="C9" s="9">
-        <f>(C7-C8)*(1+$C$6)</f>
-        <v>3082000</v>
+        <f>C7*(1+$C$6)-C8</f>
+        <v>17850000</v>
       </c>
       <c r="D9" s="9">
-        <f>(D7-D8)*(1+$C$6)</f>
-        <v>3082000</v>
+        <f>D7*(1+$C$6)-D8</f>
+        <v>17850000</v>
       </c>
       <c r="E9" s="9">
-        <f>(E7-E8)*(1+$C$6)</f>
-        <v>-4094000</v>
+        <f>E7*(1+$C$6)-E8</f>
+        <v>10674000</v>
       </c>
       <c r="F9" s="20" t="inlineStr">
         <is>
-          <t>退任予定と想定する代表者・配偶者の報酬を控除し、新体制の報酬に置換。社会保険料も概算15%で連動。常務取締役（2026/5退任）の後任要否は要確認のため対象外</t>
+          <t>譲渡時に退任する役員の報酬を全額控除（社会保険料も概算15%で連動）し、代表者の退任後の顧問料を費用計上（2026/10/19方針）</t>
         </is>
       </c>
     </row>
@@ -18420,7 +18419,7 @@
       </c>
       <c r="F10" s="20" t="inlineStr">
         <is>
-          <t>2026/3期は賞与計上なし。前2期平均相当を費用計上（仮説：支給再開を前提。不支給の経緯は要確認）</t>
+          <t>賞与規定はなく業績に応じて支給。2026/3期は支給なし。継続支給を前提に前2期平均相当を費用計上（保守的）</t>
         </is>
       </c>
     </row>
@@ -18468,7 +18467,7 @@
       </c>
       <c r="F12" s="20" t="inlineStr">
         <is>
-          <t>営業外に計上されているが、仕入完納等に伴い毎期経常的に発生する事業関連収益（受取奨励金−出荷奨励金）</t>
+          <t>営業外に計上されているが、毎期経常的に発生する事業関連収益（受取奨励金−出荷奨励金）。受取奨励金の内容は要確認</t>
         </is>
       </c>
     </row>
@@ -18480,15 +18479,15 @@
       </c>
       <c r="C13" s="19">
         <f>SUM(C9:C12)</f>
-        <v>5273508</v>
+        <v>20041508</v>
       </c>
       <c r="D13" s="19">
         <f>SUM(D9:D12)</f>
-        <v>5467707</v>
+        <v>20235707</v>
       </c>
       <c r="E13" s="19">
         <f>SUM(E9:E12)</f>
-        <v>-8388975.75</v>
+        <v>6379024.25</v>
       </c>
       <c r="F13" s="20" t="inlineStr"/>
     </row>
@@ -18500,15 +18499,15 @@
       </c>
       <c r="C14" s="13">
         <f>C5+C13</f>
-        <v>10030256</v>
+        <v>24798256</v>
       </c>
       <c r="D14" s="13">
         <f>D5+D13</f>
-        <v>1044767</v>
+        <v>15812767</v>
       </c>
       <c r="E14" s="13">
         <f>E5+E13</f>
-        <v>-2529063.75</v>
+        <v>12238936.25</v>
       </c>
       <c r="F14" s="20" t="inlineStr"/>
     </row>
@@ -18530,15 +18529,15 @@
       </c>
       <c r="C16" s="9">
         <f>-C14*$C$15</f>
-        <v>-3410287.04</v>
+        <v>-8431407.04</v>
       </c>
       <c r="D16" s="9">
         <f>-D14*$C$15</f>
-        <v>-355220.78</v>
+        <v>-5376340.78</v>
       </c>
       <c r="E16" s="9">
         <f>-E14*$C$15</f>
-        <v>859881.675</v>
+        <v>-4161238.325</v>
       </c>
       <c r="F16" s="20" t="inlineStr"/>
     </row>
@@ -18550,15 +18549,15 @@
       </c>
       <c r="C17" s="13">
         <f>C14+C16</f>
-        <v>6619968.96</v>
+        <v>16366848.96</v>
       </c>
       <c r="D17" s="13">
         <f>D14+D16</f>
-        <v>689546.22</v>
+        <v>10436426.22</v>
       </c>
       <c r="E17" s="13">
         <f>E14+E16</f>
-        <v>-1669182.075</v>
+        <v>8077697.925</v>
       </c>
       <c r="F17" s="20" t="inlineStr"/>
     </row>
@@ -18590,15 +18589,15 @@
       </c>
       <c r="C19" s="13">
         <f>C14+C18</f>
-        <v>23693940</v>
+        <v>38461940</v>
       </c>
       <c r="D19" s="13">
         <f>D14+D18</f>
-        <v>13602331</v>
+        <v>28370331</v>
       </c>
       <c r="E19" s="13">
         <f>E14+E18</f>
-        <v>6349906.25</v>
+        <v>21117906.25</v>
       </c>
       <c r="F19" s="20" t="inlineStr"/>
     </row>
@@ -18626,7 +18625,7 @@
       </c>
       <c r="E21" s="11">
         <f>SUMPRODUCT(C17:E17,C20:E20)</f>
-        <v>696266.620500001</v>
+        <v>10443146.6205</v>
       </c>
     </row>
     <row r="22">
@@ -18637,7 +18636,7 @@
       </c>
       <c r="E22" s="11">
         <f>SUMPRODUCT(C19:E19,C20:E20)</f>
-        <v>11994440.425</v>
+        <v>26762440.425</v>
       </c>
     </row>
     <row r="24">
